--- a/Semester-Planner-101-2025-fall.xlsx
+++ b/Semester-Planner-101-2025-fall.xlsx
@@ -1963,10 +1963,7 @@
       <c r="K65" s="27"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="23" t="n">
-        <f aca="false">DATE(D3,D4+3,1)</f>
-        <v>45962</v>
-      </c>
+      <c r="A66" s="0"/>
       <c r="B66" s="26"/>
       <c r="C66" s="31" t="n">
         <f aca="false">C64+1</f>
@@ -1999,6 +1996,10 @@
       <c r="K67" s="27"/>
     </row>
     <row r="68" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="23" t="n">
+        <f aca="false">DATE(D3,D4+3,1)</f>
+        <v>45962</v>
+      </c>
       <c r="B68" s="26" t="n">
         <v>11</v>
       </c>
